--- a/data/trans_orig/P1423-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2007</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>41532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126173</t>
+          <t>127684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171886</t>
+          <t>172285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177623</t>
+          <t>178263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230193</t>
+          <t>232728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>962040</t>
+          <t>961823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>990803</t>
+          <t>990191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1143227</t>
+          <t>1142828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1188940</t>
+          <t>1187429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2116642</t>
+          <t>2114107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2169212</t>
+          <t>2168572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>43688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>69719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107815</t>
+          <t>106828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99978</t>
+          <t>98436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141926</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1648869</t>
+          <t>1649725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1671009</t>
+          <t>1672191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1479858</t>
+          <t>1480845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1516057</t>
+          <t>1517954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3139160</t>
+          <t>3139301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3181108</t>
+          <t>3182650</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50121</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527695</t>
+          <t>528186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542802</t>
+          <t>542962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444274</t>
+          <t>445416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463442</t>
+          <t>463325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977699</t>
+          <t>979036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001839</t>
+          <t>1003057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226831</t>
+          <t>226997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288464</t>
+          <t>288276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324573</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398476</t>
+          <t>396959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3155332</t>
+          <t>3154036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3194048</t>
+          <t>3193871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3090733</t>
+          <t>3090921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3152366</t>
+          <t>3152200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6257265</t>
+          <t>6258782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6331168</t>
+          <t>6329194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2012</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51148</t>
+          <t>49272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84077</t>
+          <t>83884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>228900</t>
+          <t>226155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287334</t>
+          <t>284830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>290469</t>
+          <t>290928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>358484</t>
+          <t>362647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>890566</t>
+          <t>890759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>923495</t>
+          <t>925371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1050463</t>
+          <t>1052967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1108897</t>
+          <t>1111642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1953956</t>
+          <t>1949793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2021971</t>
+          <t>2021512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44934</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79281</t>
+          <t>80643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107662</t>
+          <t>107364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154173</t>
+          <t>154026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164747</t>
+          <t>163197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221717</t>
+          <t>221172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1884676</t>
+          <t>1883314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1919023</t>
+          <t>1918776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1600419</t>
+          <t>1600566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1646930</t>
+          <t>1647228</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3496832</t>
+          <t>3497377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3553802</t>
+          <t>3555352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23861</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>28717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45464</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457320</t>
+          <t>457968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474129</t>
+          <t>474424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430527</t>
+          <t>429914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448064</t>
+          <t>448069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>894349</t>
+          <t>896157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>918792</t>
+          <t>919103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117782</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168339</t>
+          <t>167214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>366737</t>
+          <t>367564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>445972</t>
+          <t>444633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>492572</t>
+          <t>499446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>587593</t>
+          <t>593168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3251443</t>
+          <t>3252568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3302000</t>
+          <t>3301146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3105048</t>
+          <t>3106387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3184283</t>
+          <t>3183456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6383208</t>
+          <t>6377633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6478229</t>
+          <t>6471355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2016</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142720</t>
+          <t>144902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192020</t>
+          <t>194098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179946</t>
+          <t>180667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237885</t>
+          <t>236105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701912</t>
+          <t>701073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>725915</t>
+          <t>725831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>802640</t>
+          <t>800562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>851940</t>
+          <t>849758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1511122</t>
+          <t>1512902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1569061</t>
+          <t>1568340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45812</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77641</t>
+          <t>76946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>149963</t>
+          <t>147513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201262</t>
+          <t>199711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204148</t>
+          <t>203621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266573</t>
+          <t>265070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1998744</t>
+          <t>1999439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2030573</t>
+          <t>2031380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1787038</t>
+          <t>1788589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1838337</t>
+          <t>1840787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3798112</t>
+          <t>3799615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3860537</t>
+          <t>3861064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527234</t>
+          <t>527914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541954</t>
+          <t>542068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518898</t>
+          <t>521148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538526</t>
+          <t>539154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053743</t>
+          <t>1054316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078816</t>
+          <t>1077168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93706</t>
+          <t>91881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134446</t>
+          <t>131811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322072</t>
+          <t>320816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>395353</t>
+          <t>396560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424927</t>
+          <t>430016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514353</t>
+          <t>519891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3243172</t>
+          <t>3245807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3283912</t>
+          <t>3285737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3136747</t>
+          <t>3135540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3210028</t>
+          <t>3211284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6395365</t>
+          <t>6389827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6484791</t>
+          <t>6479702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2023</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>68342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133076</t>
+          <t>131296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>166703</t>
+          <t>162542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181381</t>
+          <t>180388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227436</t>
+          <t>222192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445021</t>
+          <t>446596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472750</t>
+          <t>471634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>588805</t>
+          <t>592966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>622432</t>
+          <t>624212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1043010</t>
+          <t>1048254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1089065</t>
+          <t>1090058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75329</t>
+          <t>72752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133222</t>
+          <t>134134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155914</t>
+          <t>162228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255903</t>
+          <t>253074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>265300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373844</t>
+          <t>374527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2157105</t>
+          <t>2156193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2214998</t>
+          <t>2217575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1981920</t>
+          <t>1984749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2081909</t>
+          <t>2075595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4154306</t>
+          <t>4153623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4273115</t>
+          <t>4262850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49101</t>
+          <t>48705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60948</t>
+          <t>61352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>65290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99886</t>
+          <t>100892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597522</t>
+          <t>597918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623395</t>
+          <t>623765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599515</t>
+          <t>599111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623185</t>
+          <t>623608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207200</t>
+          <t>1206194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1242363</t>
+          <t>1241796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155327</t>
+          <t>148591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232009</t>
+          <t>229004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>336075</t>
+          <t>336824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455830</t>
+          <t>456287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>530864</t>
+          <t>528253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>667536</t>
+          <t>673333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3219880</t>
+          <t>3222885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3296562</t>
+          <t>3303298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3197964</t>
+          <t>3197507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3317719</t>
+          <t>3316970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6438147</t>
+          <t>6432350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6574819</t>
+          <t>6577430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1423-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>41594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>70644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127684</t>
+          <t>126221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172285</t>
+          <t>170981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178263</t>
+          <t>178441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232728</t>
+          <t>232674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961823</t>
+          <t>961079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>990191</t>
+          <t>990129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1142828</t>
+          <t>1144132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1187429</t>
+          <t>1188892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2114107</t>
+          <t>2114161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2168572</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>22120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43688</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69719</t>
+          <t>70683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106828</t>
+          <t>106952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +1126,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>119674</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>101050</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>143912</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>4,39%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>119674</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>98436</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>141785</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1649725</t>
+          <t>1649614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1672191</t>
+          <t>1671293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1480845</t>
+          <t>1480721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1517954</t>
+          <t>1516990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1239,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3161412</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3137174</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3180036</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>95,61%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3087</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3161412</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3139301</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3182650</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528186</t>
+          <t>528527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542962</t>
+          <t>542294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445416</t>
+          <t>446078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463325</t>
+          <t>464411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>979036</t>
+          <t>977813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1003057</t>
+          <t>1003099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>121468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288276</t>
+          <t>284522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326547</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>396959</t>
+          <t>393864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3154036</t>
+          <t>3155075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3193871</t>
+          <t>3193277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3090921</t>
+          <t>3094675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3152200</t>
+          <t>3157168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6258782</t>
+          <t>6261877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6329194</t>
+          <t>6337474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83884</t>
+          <t>84639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226155</t>
+          <t>228856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284830</t>
+          <t>288663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>290928</t>
+          <t>291403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362647</t>
+          <t>361327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>890759</t>
+          <t>890004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>925371</t>
+          <t>923707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1052967</t>
+          <t>1049134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1111642</t>
+          <t>1108941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1949793</t>
+          <t>1951113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2021512</t>
+          <t>2021037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>44709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80643</t>
+          <t>79358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107364</t>
+          <t>109039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154026</t>
+          <t>153452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163197</t>
+          <t>162863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221172</t>
+          <t>218003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1883314</t>
+          <t>1884599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1918776</t>
+          <t>1919248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1600566</t>
+          <t>1601140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1647228</t>
+          <t>1645553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3497377</t>
+          <t>3500546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3555352</t>
+          <t>3555686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28717</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>44011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457968</t>
+          <t>456950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474424</t>
+          <t>474255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429914</t>
+          <t>430662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448069</t>
+          <t>448923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896157</t>
+          <t>895802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>919103</t>
+          <t>919358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>118636</t>
+          <t>116140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167214</t>
+          <t>166870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>367564</t>
+          <t>367574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444633</t>
+          <t>443427</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499446</t>
+          <t>499630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>593168</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3252568</t>
+          <t>3252912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3301146</t>
+          <t>3303642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3106387</t>
+          <t>3107593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3183456</t>
+          <t>3183446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6377633</t>
+          <t>6376504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6471355</t>
+          <t>6471171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144902</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194098</t>
+          <t>191787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180667</t>
+          <t>180832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236105</t>
+          <t>236716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701073</t>
+          <t>701121</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>725831</t>
+          <t>725076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>800562</t>
+          <t>802873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>849758</t>
+          <t>849963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1512902</t>
+          <t>1512291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1568340</t>
+          <t>1568175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76946</t>
+          <t>77604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147513</t>
+          <t>149546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199711</t>
+          <t>200339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203621</t>
+          <t>205569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>265070</t>
+          <t>268014</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1999439</t>
+          <t>1998781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2031380</t>
+          <t>2029959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1788589</t>
+          <t>1787961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1840787</t>
+          <t>1838754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3799615</t>
+          <t>3796671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3861064</t>
+          <t>3859116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>20231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27992</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527914</t>
+          <t>526655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542068</t>
+          <t>541911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521148</t>
+          <t>520790</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539154</t>
+          <t>538926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054316</t>
+          <t>1053591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077168</t>
+          <t>1077575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91881</t>
+          <t>91405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131811</t>
+          <t>135709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>320816</t>
+          <t>321124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>396560</t>
+          <t>397819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430016</t>
+          <t>427283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519891</t>
+          <t>514294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3245807</t>
+          <t>3241909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3285737</t>
+          <t>3286213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3135540</t>
+          <t>3134281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3211284</t>
+          <t>3210976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6389827</t>
+          <t>6395424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6479702</t>
+          <t>6482435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>57107</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>70781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>147236</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131296</t>
+          <t>146079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162542</t>
+          <t>180466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>201949</t>
+          <t>220640</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180388</t>
+          <t>196525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222192</t>
+          <t>243625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>460226</t>
+          <t>521422</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446596</t>
+          <t>507748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>471634</t>
+          <t>533714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>608272</t>
+          <t>658505</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592966</t>
+          <t>641572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>624212</t>
+          <t>675959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1068497</t>
+          <t>1179927</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1048254</t>
+          <t>1156942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1090058</t>
+          <t>1204042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>120124</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72752</t>
+          <t>100403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134134</t>
+          <t>143766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>217897</t>
+          <t>239609</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162228</t>
+          <t>213341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253074</t>
+          <t>265143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>326876</t>
+          <t>359733</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265300</t>
+          <t>330974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374527</t>
+          <t>396450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2181348</t>
+          <t>2110442</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2156193</t>
+          <t>2086800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2217575</t>
+          <t>2130163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2019926</t>
+          <t>1931783</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1984749</t>
+          <t>1906249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2075595</t>
+          <t>1958051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4201274</t>
+          <t>4042226</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4153623</t>
+          <t>4005509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4262850</t>
+          <t>4070985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48705</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61352</t>
+          <t>65446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81079</t>
+          <t>90636</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65290</t>
+          <t>73407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100892</t>
+          <t>111036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>612947</t>
+          <t>673771</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597918</t>
+          <t>658800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623765</t>
+          <t>685104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>613059</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599111</t>
+          <t>669431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623608</t>
+          <t>694364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1226007</t>
+          <t>1355828</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1206194</t>
+          <t>1335428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1241796</t>
+          <t>1373057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148591</t>
+          <t>186300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229004</t>
+          <t>247141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>412537</t>
+          <t>455962</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>336824</t>
+          <t>421420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456287</t>
+          <t>488850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>609904</t>
+          <t>671009</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>528253</t>
+          <t>628318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>673333</t>
+          <t>715440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3254522</t>
+          <t>3305636</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3222885</t>
+          <t>3273542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3303298</t>
+          <t>3334383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3241257</t>
+          <t>3272345</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3197507</t>
+          <t>3239457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3316970</t>
+          <t>3306887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6495779</t>
+          <t>6577981</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6432350</t>
+          <t>6533550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6577430</t>
+          <t>6620672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
